--- a/1-examen/Libro3.xlsx
+++ b/1-examen/Libro3.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\upateco\PowerBi-Upateco\primer examen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0-PowerBI_Agosto\PrimerParcial\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C521791-A6F2-4829-B4A2-D037C92CBE80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11010"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{980ABF85-C4B2-4B82-8E73-F27AC6001323}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -83,7 +84,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
   </numFmts>
@@ -532,7 +533,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7A71DEB-292A-4B57-A7F2-84C02B946584}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
